--- a/docs/i18n/strings.xlsx
+++ b/docs/i18n/strings.xlsx
@@ -36907,22 +36907,22 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Select category</t>
+          <t>Select department</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>병원 구분 선택</t>
+          <t>진료과 선택</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>اختر الفئة</t>
+          <t>اختر التخصص</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>病院区分を選択</t>
+          <t>診療科を選択</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">

--- a/docs/i18n/strings.xlsx
+++ b/docs/i18n/strings.xlsx
@@ -39403,22 +39403,22 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Hospital category</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>병원 구분</t>
+          <t>진료과</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>تصنيف المستشفى</t>
+          <t>التخصص</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>病院区分</t>
+          <t>診療科</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
